--- a/docs/hub/estate/Planning and Insight/Data Requests/Data request log.xlsx
+++ b/docs/hub/estate/Planning and Insight/Data Requests/Data request log.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Done (declined)</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Education has no NSS finalists. Pointed to enrolment survey instead. Requester not pleased.</t>
+          <t>Supplied. Noted that Education's A and F went up; the Faculty fall is Health. Requester still worried.</t>
         </is>
       </c>
     </row>
